--- a/英语群_20260812.xlsx
+++ b/英语群_20260812.xlsx
@@ -1258,15 +1258,15 @@
       </c>
       <c r="C1" s="24">
         <f>SUM(C3:C1001)</f>
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D1" s="24">
         <f>SUM(D3:D1001)</f>
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E1" s="24">
         <f>SUM(E3:E1001)</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>0</v>
@@ -1452,21 +1452,21 @@
       </c>
       <c r="C6" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="F6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -1494,21 +1494,21 @@
       </c>
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="F7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C9" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3">
         <f t="shared" si="2"/>
@@ -1586,16 +1586,16 @@
       </c>
       <c r="E9" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="25">
         <v>10</v>
@@ -1624,20 +1624,20 @@
       </c>
       <c r="D10" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="25">
         <v>9</v>
@@ -1830,21 +1830,21 @@
       </c>
       <c r="C15" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5">
         <v>0</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C16" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="3">
         <f t="shared" si="2"/>
@@ -1880,16 +1880,16 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5">
         <v>0</v>
       </c>
       <c r="H16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="25">
         <v>11</v>
@@ -1960,20 +1960,20 @@
       </c>
       <c r="D18" s="3">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5">
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="25">
         <v>4</v>
@@ -2044,20 +2044,20 @@
       </c>
       <c r="D20" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" s="5">
         <v>0</v>
       </c>
       <c r="G20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="25">
         <v>11</v>
@@ -2460,21 +2460,21 @@
       </c>
       <c r="C30" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" s="3">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="3">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="F30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="5">
         <v>0</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="C32" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" s="3">
         <f t="shared" si="2"/>
@@ -2552,16 +2552,16 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="5">
         <v>0</v>
       </c>
       <c r="H32" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="25">
         <v>11</v>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C35" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" s="3">
         <f t="shared" si="2"/>
@@ -2678,16 +2678,16 @@
       </c>
       <c r="E35" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="5">
         <v>0</v>
       </c>
       <c r="H35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="25">
         <v>10</v>
@@ -2838,21 +2838,21 @@
       </c>
       <c r="C39" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" s="3">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F39" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="5">
         <v>0</v>
@@ -2884,20 +2884,20 @@
       </c>
       <c r="D40" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F40" s="5">
         <v>0</v>
       </c>
       <c r="G40" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="25">
         <v>10</v>
@@ -3178,20 +3178,20 @@
       </c>
       <c r="D47" s="3">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="3">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="5">
         <v>0</v>
       </c>
       <c r="G47" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="25">
         <v>8</v>
@@ -3216,21 +3216,21 @@
       </c>
       <c r="C48" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="5">
         <v>0</v>

--- a/英语群_20260812.xlsx
+++ b/英语群_20260812.xlsx
@@ -1258,15 +1258,15 @@
       </c>
       <c r="C1" s="24">
         <f>SUM(C3:C1001)</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D1" s="24">
         <f>SUM(D3:D1001)</f>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E1" s="24">
         <f>SUM(E3:E1001)</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>0</v>
@@ -1368,21 +1368,21 @@
       </c>
       <c r="C4" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="F4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" si="2"/>
@@ -1502,16 +1502,16 @@
       </c>
       <c r="E7" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
       </c>
       <c r="H7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="25">
         <v>11</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C10" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" si="2"/>
@@ -1628,16 +1628,16 @@
       </c>
       <c r="E10" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
       </c>
       <c r="H10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="25">
         <v>9</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C15" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="2"/>
@@ -1838,16 +1838,16 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5">
         <v>0</v>
       </c>
       <c r="H15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="25">
         <v>11</v>
@@ -1872,21 +1872,21 @@
       </c>
       <c r="C16" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="5">
         <v>0</v>
@@ -1960,20 +1960,20 @@
       </c>
       <c r="D18" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="5">
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="25">
         <v>4</v>
@@ -2044,20 +2044,20 @@
       </c>
       <c r="D20" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="5">
         <v>0</v>
       </c>
       <c r="G20" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="25">
         <v>11</v>
@@ -2334,21 +2334,21 @@
       </c>
       <c r="C27" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="3">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="5">
         <v>0</v>
@@ -2418,21 +2418,21 @@
       </c>
       <c r="C29" s="3">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="3">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="F29" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="5">
         <v>0</v>
@@ -2544,21 +2544,21 @@
       </c>
       <c r="C32" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" s="3">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="3">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="F32" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="5">
         <v>0</v>
@@ -2712,21 +2712,21 @@
       </c>
       <c r="C36" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="3">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="F36" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="5">
         <v>0</v>
@@ -2796,21 +2796,21 @@
       </c>
       <c r="C38" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="3">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="F38" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="5">
         <v>0</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="C40" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" s="3">
         <f t="shared" si="2"/>
@@ -2888,16 +2888,16 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="5">
         <v>0</v>
       </c>
       <c r="H40" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="25">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C47" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D47" s="3">
         <f t="shared" si="2"/>
@@ -3182,16 +3182,16 @@
       </c>
       <c r="E47" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="5">
         <v>0</v>
       </c>
       <c r="H47" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="25">
         <v>8</v>
@@ -3216,21 +3216,21 @@
       </c>
       <c r="C48" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F48" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="5">
         <v>0</v>
@@ -3262,20 +3262,20 @@
       </c>
       <c r="D49" s="3">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E49" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
       </c>
       <c r="G49" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="25">
         <v>11</v>
